--- a/nr-update-valueset/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T14:32:05+00:00</t>
+    <t>2024-03-06T16:49:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/nr-update-valueset/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$70</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2139" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2413" uniqueCount="446">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T16:49:12+00:00</t>
+    <t>2024-03-07T12:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -689,6 +689,195 @@
     <t>Identifiant fonctionnel, numéro d'autorisation ARHGOS (numeroAutorisationARHGOS).</t>
   </si>
   <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.use</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.type</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.system</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>https://arhgos.ars.sante.fr/</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.value</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.period</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.assigner</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
     <t>HealthcareService.active</t>
   </si>
   <si>
@@ -730,10 +919,6 @@
     <t>This property is recommended to be the same as the Location's managingOrganization, and if not provided should be interpreted as such. If the Location does not have a managing Organization, then this property should be populated.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>.scopingRole.Organization</t>
   </si>
   <si>
@@ -744,10 +929,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
     <t>La modalité étant un mode d’application ou un type de soin prévu par les textes réglementaires encadrant chaque activité de soins (modalite).</t>
   </si>
   <si>
@@ -755,9 +936,6 @@
   </si>
   <si>
     <t>Selecting a Service Category then determines the list of relevant service types that can be selected in the primary service type.</t>
-  </si>
-  <si>
-    <t>required</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J132-ModaliteActivite-RASS/FHIR/JDV-J132-ModaliteActivite-RASS</t>
@@ -1197,22 +1375,10 @@
     <t>HealthcareService.notAvailable.during</t>
   </si>
   <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
     <t>Service not available from this date</t>
   </si>
   <si>
     <t>Service is not available (seasonally or for a public holiday) from this date.</t>
-  </si>
-  <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>HealthcareService.availabilityExceptions</t>
@@ -1554,7 +1720,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL62"/>
+  <dimension ref="A1:AL70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="63.55078125" customWidth="true" bestFit="true"/>
@@ -1576,7 +1742,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
@@ -1592,7 +1758,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="72.5234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -3979,7 +4145,7 @@
         <v>215</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3996,30 +4162,26 @@
         <v>75</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>216</v>
+        <v>100</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>217</v>
+        <v>101</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q23" t="s" s="2">
-        <v>220</v>
-      </c>
+      <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
         <v>75</v>
       </c>
@@ -4063,7 +4225,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>215</v>
+        <v>103</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4072,56 +4234,56 @@
         <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>221</v>
+        <v>104</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>222</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>224</v>
+        <v>107</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>225</v>
+        <v>108</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>226</v>
+        <v>109</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>227</v>
+        <v>110</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4159,34 +4321,34 @@
         <v>75</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>223</v>
+        <v>114</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>228</v>
+        <v>115</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>75</v>
@@ -4194,44 +4356,46 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I25" t="s" s="2">
         <v>85</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>232</v>
+        <v>168</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>223</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>75</v>
       </c>
@@ -4255,11 +4419,13 @@
         <v>75</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>225</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -4277,13 +4443,13 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>96</v>
@@ -4292,29 +4458,29 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>239</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>241</v>
+        <v>75</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>75</v>
@@ -4329,15 +4495,17 @@
         <v>232</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
       </c>
@@ -4361,11 +4529,13 @@
         <v>75</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>237</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>75</v>
@@ -4383,13 +4553,13 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>96</v>
@@ -4398,7 +4568,7 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>75</v>
@@ -4406,10 +4576,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4417,13 +4587,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>75</v>
@@ -4432,18 +4602,20 @@
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>232</v>
+        <v>133</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="N27" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="O27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
       </c>
@@ -4452,10 +4624,10 @@
         <v>75</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>75</v>
+        <v>246</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>75</v>
+        <v>247</v>
       </c>
       <c r="U27" t="s" s="2">
         <v>75</v>
@@ -4467,11 +4639,13 @@
         <v>75</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>75</v>
@@ -4489,13 +4663,13 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>96</v>
@@ -4504,7 +4678,7 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>75</v>
@@ -4512,7 +4686,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>251</v>
@@ -4526,7 +4700,7 @@
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>75</v>
@@ -4538,16 +4712,16 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4561,7 +4735,7 @@
         <v>75</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>75</v>
+        <v>255</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>75</v>
@@ -4597,25 +4771,25 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>228</v>
+        <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>257</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" hidden="true">
@@ -4623,7 +4797,7 @@
         <v>258</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4646,16 +4820,16 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>100</v>
+        <v>260</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4705,7 +4879,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4717,10 +4891,10 @@
         <v>96</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>265</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>75</v>
@@ -4728,10 +4902,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4754,16 +4928,16 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>100</v>
+        <v>269</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4813,7 +4987,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4825,10 +4999,10 @@
         <v>96</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>274</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>75</v>
@@ -4836,10 +5010,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4856,28 +5030,30 @@
         <v>75</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q31" s="2"/>
+      <c r="Q31" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="R31" t="s" s="2">
         <v>75</v>
       </c>
@@ -4921,7 +5097,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4936,18 +5112,18 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>75</v>
+        <v>283</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4961,7 +5137,7 @@
         <v>84</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>75</v>
@@ -4970,16 +5146,16 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5029,7 +5205,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5041,10 +5217,10 @@
         <v>96</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>75</v>
@@ -5052,14 +5228,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>75</v>
+        <v>291</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5069,25 +5245,25 @@
         <v>77</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>282</v>
+        <v>232</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5113,13 +5289,11 @@
         <v>75</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>75</v>
+        <v>295</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>75</v>
@@ -5137,7 +5311,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5149,25 +5323,25 @@
         <v>96</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>286</v>
+        <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>75</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>75</v>
+        <v>299</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5183,19 +5357,19 @@
         <v>75</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5221,13 +5395,11 @@
         <v>75</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="Y34" s="2"/>
       <c r="Z34" t="s" s="2">
-        <v>75</v>
+        <v>303</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>75</v>
@@ -5245,7 +5417,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5257,10 +5429,10 @@
         <v>96</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>228</v>
+        <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>75</v>
@@ -5268,10 +5440,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5285,25 +5457,25 @@
         <v>77</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
         <v>232</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5329,13 +5501,11 @@
         <v>75</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="Y35" s="2"/>
       <c r="Z35" t="s" s="2">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -5353,7 +5523,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5368,7 +5538,7 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>75</v>
@@ -5376,10 +5546,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5399,18 +5569,20 @@
         <v>75</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>75</v>
@@ -5459,7 +5631,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5471,21 +5643,21 @@
         <v>96</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>97</v>
+        <v>274</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>104</v>
+        <v>314</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>75</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5505,18 +5677,20 @@
         <v>75</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>100</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>101</v>
+        <v>317</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>318</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>319</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>75</v>
@@ -5565,7 +5739,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>103</v>
+        <v>316</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5574,13 +5748,13 @@
         <v>84</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>104</v>
+        <v>320</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>75</v>
@@ -5588,21 +5762,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>75</v>
@@ -5611,19 +5785,19 @@
         <v>75</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>108</v>
+        <v>322</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>109</v>
+        <v>323</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>110</v>
+        <v>324</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5661,34 +5835,34 @@
         <v>75</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>114</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>98</v>
+        <v>325</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>75</v>
@@ -5696,46 +5870,44 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>306</v>
+        <v>75</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>107</v>
+        <v>327</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
       </c>
@@ -5783,22 +5955,22 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>98</v>
+        <v>331</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>75</v>
@@ -5806,10 +5978,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5829,19 +6001,19 @@
         <v>75</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>232</v>
+        <v>333</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>244</v>
+        <v>336</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5867,10 +6039,10 @@
         <v>75</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>313</v>
+        <v>75</v>
       </c>
       <c r="Z40" t="s" s="2">
         <v>75</v>
@@ -5891,7 +6063,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5903,10 +6075,10 @@
         <v>96</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>97</v>
+        <v>337</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>298</v>
+        <v>338</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>75</v>
@@ -5914,10 +6086,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5928,7 +6100,7 @@
         <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>75</v>
@@ -5940,16 +6112,16 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>269</v>
+        <v>340</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5999,22 +6171,22 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>97</v>
+        <v>344</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>318</v>
+        <v>345</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>75</v>
@@ -6022,10 +6194,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6048,16 +6220,16 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>232</v>
+        <v>310</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6083,13 +6255,13 @@
         <v>75</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>323</v>
+        <v>75</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>324</v>
+        <v>75</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>75</v>
@@ -6107,7 +6279,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6119,10 +6291,10 @@
         <v>96</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>97</v>
+        <v>274</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>75</v>
@@ -6130,10 +6302,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6147,7 +6319,7 @@
         <v>77</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>75</v>
@@ -6159,13 +6331,13 @@
         <v>232</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>327</v>
+        <v>352</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>328</v>
+        <v>353</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6191,11 +6363,13 @@
         <v>75</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -6213,7 +6387,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6228,7 +6402,7 @@
         <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>325</v>
+        <v>356</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>75</v>
@@ -6236,10 +6410,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6262,17 +6436,15 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>232</v>
+        <v>358</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6297,13 +6469,13 @@
         <v>75</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>174</v>
+        <v>75</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
@@ -6321,7 +6493,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6336,7 +6508,7 @@
         <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>335</v>
+        <v>104</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -6344,10 +6516,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>336</v>
+        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6358,7 +6530,7 @@
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>75</v>
@@ -6370,17 +6542,15 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>232</v>
+        <v>100</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>337</v>
+        <v>101</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>75</v>
@@ -6405,13 +6575,13 @@
         <v>75</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>339</v>
+        <v>75</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>340</v>
+        <v>75</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>75</v>
@@ -6429,22 +6599,22 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>336</v>
+        <v>103</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>325</v>
+        <v>104</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>75</v>
@@ -6452,21 +6622,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>75</v>
@@ -6478,15 +6648,17 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>216</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>342</v>
+        <v>108</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>110</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>75</v>
@@ -6523,34 +6695,34 @@
         <v>75</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>341</v>
+        <v>114</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>325</v>
+        <v>98</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>75</v>
@@ -6558,14 +6730,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>75</v>
+        <v>364</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6578,24 +6750,26 @@
         <v>75</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>300</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>345</v>
+        <v>365</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>202</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>75</v>
       </c>
@@ -6643,7 +6817,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6655,10 +6829,10 @@
         <v>96</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>348</v>
+        <v>98</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>75</v>
@@ -6666,10 +6840,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>349</v>
+        <v>368</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6692,15 +6866,17 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>100</v>
+        <v>232</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>101</v>
+        <v>369</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -6725,10 +6901,10 @@
         <v>75</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>75</v>
+        <v>371</v>
       </c>
       <c r="Z48" t="s" s="2">
         <v>75</v>
@@ -6749,7 +6925,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>103</v>
+        <v>368</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6758,13 +6934,13 @@
         <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>104</v>
+        <v>356</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
@@ -6772,21 +6948,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>75</v>
@@ -6798,16 +6974,16 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>107</v>
+        <v>327</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>108</v>
+        <v>373</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>109</v>
+        <v>374</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>110</v>
+        <v>375</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -6845,34 +7021,34 @@
         <v>75</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>114</v>
+        <v>372</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>98</v>
+        <v>376</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>75</v>
@@ -6880,14 +7056,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>306</v>
+        <v>75</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6900,26 +7076,24 @@
         <v>75</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>107</v>
+        <v>232</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>307</v>
+        <v>378</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>308</v>
+        <v>379</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>202</v>
-      </c>
+        <v>380</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>75</v>
       </c>
@@ -6943,13 +7117,13 @@
         <v>75</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>75</v>
+        <v>381</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>75</v>
+        <v>382</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>75</v>
@@ -6967,7 +7141,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>309</v>
+        <v>377</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6979,10 +7153,10 @@
         <v>96</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>98</v>
+        <v>383</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>75</v>
@@ -6990,10 +7164,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7007,7 +7181,7 @@
         <v>77</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>75</v>
@@ -7016,16 +7190,16 @@
         <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>168</v>
+        <v>232</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>354</v>
+        <v>386</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>261</v>
+        <v>387</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7051,13 +7225,11 @@
         <v>75</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>356</v>
+        <v>388</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -7075,7 +7247,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7090,7 +7262,7 @@
         <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>348</v>
+        <v>383</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>75</v>
@@ -7098,10 +7270,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7112,7 +7284,7 @@
         <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>75</v>
@@ -7124,15 +7296,17 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>358</v>
+        <v>390</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>75</v>
@@ -7157,13 +7331,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>75</v>
+        <v>173</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>75</v>
+        <v>174</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -7181,13 +7355,13 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>96</v>
@@ -7196,7 +7370,7 @@
         <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>348</v>
+        <v>393</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>75</v>
@@ -7204,10 +7378,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7218,7 +7392,7 @@
         <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>75</v>
@@ -7230,16 +7404,16 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>361</v>
+        <v>232</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>362</v>
+        <v>395</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>364</v>
+        <v>302</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7265,13 +7439,13 @@
         <v>75</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>75</v>
+        <v>397</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>75</v>
+        <v>398</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>75</v>
@@ -7289,13 +7463,13 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>360</v>
+        <v>394</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>96</v>
@@ -7304,7 +7478,7 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>348</v>
+        <v>383</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>75</v>
@@ -7312,10 +7486,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7338,17 +7512,15 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>361</v>
+        <v>277</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>366</v>
+        <v>400</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>75</v>
@@ -7397,7 +7569,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7412,7 +7584,7 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>348</v>
+        <v>383</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>75</v>
@@ -7420,10 +7592,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7446,15 +7618,17 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>300</v>
+        <v>358</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>369</v>
+        <v>403</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>404</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>405</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>75</v>
@@ -7503,7 +7677,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>368</v>
+        <v>402</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7518,7 +7692,7 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>348</v>
+        <v>406</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>75</v>
@@ -7526,10 +7700,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>371</v>
+        <v>407</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>371</v>
+        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7632,10 +7806,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>372</v>
+        <v>408</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>372</v>
+        <v>408</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7740,14 +7914,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>373</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>373</v>
+        <v>409</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>306</v>
+        <v>364</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7769,10 +7943,10 @@
         <v>107</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>307</v>
+        <v>365</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>308</v>
+        <v>366</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>110</v>
@@ -7827,7 +8001,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>309</v>
+        <v>367</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -7850,10 +8024,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7861,10 +8035,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>75</v>
@@ -7876,16 +8050,16 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>375</v>
+        <v>411</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>376</v>
+        <v>412</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>261</v>
+        <v>319</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7911,13 +8085,13 @@
         <v>75</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>75</v>
+        <v>413</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>75</v>
+        <v>414</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>75</v>
@@ -7935,13 +8109,13 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>374</v>
+        <v>410</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>96</v>
@@ -7950,7 +8124,7 @@
         <v>97</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>104</v>
+        <v>406</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>75</v>
@@ -7958,10 +8132,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7984,17 +8158,15 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>378</v>
+        <v>277</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>379</v>
+        <v>416</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>75</v>
@@ -8043,7 +8215,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>377</v>
+        <v>415</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8055,10 +8227,10 @@
         <v>96</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>382</v>
+        <v>97</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>348</v>
+        <v>406</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>75</v>
@@ -8066,10 +8238,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>383</v>
+        <v>418</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>383</v>
+        <v>418</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8092,16 +8264,16 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>100</v>
+        <v>419</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>261</v>
+        <v>422</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8151,7 +8323,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>383</v>
+        <v>418</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -8166,7 +8338,7 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>348</v>
+        <v>406</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>75</v>
@@ -8174,10 +8346,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>386</v>
+        <v>423</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>386</v>
+        <v>423</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8188,7 +8360,7 @@
         <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>75</v>
@@ -8200,16 +8372,16 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>387</v>
+        <v>419</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>255</v>
+        <v>422</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8259,29 +8431,891 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>386</v>
+        <v>423</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>228</v>
+        <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AL70" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL62">
+  <autoFilter ref="A1:AL70">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8291,7 +9325,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI61">
+  <conditionalFormatting sqref="A2:AI69">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/nr-update-valueset/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-healthcareservice-healthcare-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T12:17:43+00:00</t>
+    <t>2024-03-07T12:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
